--- a/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
+++ b/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
@@ -1040,7 +1040,7 @@
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
